--- a/Game/Religion.xlsx
+++ b/Game/Religion.xlsx
@@ -71,7 +71,7 @@
     <t xml:space="preserve">eyth</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.252 Patch 2</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">Eyth of Void</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">Nguyệt Ảnh,Horome</t>
   </si>
   <si>
-    <t xml:space="preserve">Chiến Tranh,Yevan</t>
+    <t xml:space="preserve">Xung Đột,Yevan</t>
   </si>
 </sst>
 </file>
